--- a/data/trending_integrated_20260921_14.xlsx
+++ b/data/trending_integrated_20260921_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G2" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204024373535</v>
+        <v>204073409035</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10880</v>
+        <v>10800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.62%</t>
+          <t>'+19.73%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>246647161290</v>
+        <v>249896199340</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21400</v>
+        <v>21250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.86%</t>
+          <t>'+15.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>105159530470</v>
+        <v>110621107895</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스, 혈관 치료 기술 확장 및 글로벌 3상 돌입. MSD 인수 영향 및 보호예수 관련 언급.</t>
+          <t>혈관 치료 기술 확장 및 글로벌 3상 동시 돌입. 대규모 인수합병 사례 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['혈관치료', '글로벌3상', 'MSD인수']</t>
+          <t>['혈관 치료', 'ADC', '인수합병']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32050</v>
+        <v>32000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.09%</t>
+          <t>'+7.93%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="F5" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G5" t="n">
-        <v>2152</v>
+        <v>2184</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>38328486500</v>
+        <v>38913028675</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5810</v>
+        <v>5830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.00%</t>
+          <t>'+7.37%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H6" t="n">
         <v>0.19</v>
@@ -978,7 +978,7 @@
         <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>61574836780</v>
+        <v>61673048160</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>209000</v>
+        <v>11190</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.58%</t>
+          <t>'+6.37%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.09</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="G7" t="n">
-        <v>495</v>
+        <v>434</v>
       </c>
       <c r="H7" t="n">
-        <v>75.44</v>
+        <v>18.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>196100</v>
+        <v>10520</v>
       </c>
       <c r="K7" t="n">
-        <v>199800</v>
+        <v>10780</v>
       </c>
       <c r="L7" t="n">
-        <v>209000</v>
+        <v>12190</v>
       </c>
       <c r="M7" t="n">
-        <v>199600</v>
+        <v>10590</v>
       </c>
       <c r="N7" t="n">
-        <v>75.53</v>
+        <v>18.13</v>
       </c>
       <c r="O7" t="n">
-        <v>678920210050</v>
+        <v>203098141910</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>64700</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>652000</v>
+        <v>-70000</v>
       </c>
       <c r="S7" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인 수급 집중 및 연말 배당 기대감. 52주 신고가 돌파 및 30만원 목표.</t>
+          <t>광통신주 급등 및 연기금 매수세 유입. 공시 기대감 속 11500원 돌파 및 2만원 목표.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['우선주', '외인 수급', '배당 기대']</t>
+          <t>['광통신', '연기금', '공시']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11210</v>
+        <v>208000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
-        <v>431</v>
+        <v>547</v>
       </c>
       <c r="H8" t="n">
-        <v>18.29</v>
+        <v>75.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10520</v>
+        <v>196100</v>
       </c>
       <c r="K8" t="n">
-        <v>10780</v>
+        <v>199800</v>
       </c>
       <c r="L8" t="n">
-        <v>12190</v>
+        <v>209000</v>
       </c>
       <c r="M8" t="n">
-        <v>10590</v>
+        <v>199600</v>
       </c>
       <c r="N8" t="n">
-        <v>18.13</v>
+        <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>201875542815</v>
+        <v>701027871300</v>
       </c>
       <c r="P8" t="n">
-        <v>22450</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>64700</v>
       </c>
       <c r="R8" t="n">
-        <v>-70000</v>
+        <v>652000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>광통신주 급등 및 연기금 매수세 유입. 공시 기대감 속 11500원 돌파 및 2만원 목표.</t>
+          <t>외인 수급 집중 및 연말 배당 기대감. 52주 신고가 돌파 및 30만원 목표.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '연기금', '공시']</t>
+          <t>['우선주', '외인 수급', '배당 기대']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>273500</v>
+        <v>273000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.79%</t>
+          <t>'+4.60%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G9" t="n">
-        <v>2683</v>
+        <v>2642</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4581454914250</v>
+        <v>4702624235500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성전자, 외인 매수세 유입에도 정치적 불확실성 언급. BNK증권 목표가 하향 및 배당금 기대.</t>
+          <t>외인 매수세 유입 확인 및 배당금 지급 예정. 증권사 목표가 하향 조정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인매수', '목표가', '배당금']</t>
+          <t>['외인 매수', '배당금', '목표가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1873000</v>
+        <v>1871000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.86%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G10" t="n">
-        <v>2295</v>
+        <v>2267</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3653496462500</v>
+        <v>3754813832000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, 신한증권 앱 오류 발생 속 반도체 수출 호조 기대. 193만 돌파 시 상승 전망.</t>
+          <t>반도체 수출 호조 기대감 속 개인 투자자 매도에 대한 언급. 증권사 앱 오류 발생.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체수출', '신한증권', '상승전망']</t>
+          <t>['반도체 수출', '개인 매도', '증권사 앱']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26300</v>
+        <v>26150</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-2.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>120664906250</v>
+        <v>122050446600</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13550</v>
+        <v>13480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.31%</t>
+          <t>'-2.81%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
         <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="H12" t="n">
         <v>5.5</v>
@@ -1524,13 +1524,13 @@
         <v>14790</v>
       </c>
       <c r="M12" t="n">
-        <v>13500</v>
+        <v>13460</v>
       </c>
       <c r="N12" t="n">
         <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>69330354350</v>
+        <v>70601625720</v>
       </c>
       <c r="P12" t="n">
         <v>30200</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>77800</v>
+        <v>18360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="F13" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>743</v>
+        <v>441</v>
       </c>
       <c r="H13" t="n">
-        <v>10.58</v>
+        <v>10.74</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>80000</v>
+        <v>18910</v>
       </c>
       <c r="K13" t="n">
-        <v>82900</v>
+        <v>19050</v>
       </c>
       <c r="L13" t="n">
-        <v>83000</v>
+        <v>19050</v>
       </c>
       <c r="M13" t="n">
-        <v>75300</v>
+        <v>18090</v>
       </c>
       <c r="N13" t="n">
-        <v>10.68</v>
+        <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>104197515250</v>
+        <v>74869712160</v>
       </c>
       <c r="P13" t="n">
-        <v>184000</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>44750</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-556000</v>
+        <v>-698000</v>
       </c>
       <c r="S13" t="n">
-        <v>-46000</v>
+        <v>-184000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
+          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 주가 상승 억제 및 대차해지 운동 주장.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['드론', 'K-방산', '공매도']</t>
+          <t>['공매도', '대차해지', '장부 조작']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18360</v>
+        <v>317250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-2.98%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E14" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F14" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>432</v>
+        <v>256</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74</v>
+        <v>3.62</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,143 +1699,143 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18910</v>
+        <v>327000</v>
       </c>
       <c r="K14" t="n">
-        <v>19050</v>
+        <v>324000</v>
       </c>
       <c r="L14" t="n">
-        <v>19050</v>
+        <v>340500</v>
       </c>
       <c r="M14" t="n">
-        <v>18090</v>
+        <v>308500</v>
       </c>
       <c r="N14" t="n">
-        <v>10.74</v>
+        <v>1.96</v>
       </c>
       <c r="O14" t="n">
-        <v>73923174325</v>
+        <v>89249039000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>635000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>52600</v>
       </c>
       <c r="R14" t="n">
-        <v>-698000</v>
+        <v>-62000</v>
       </c>
       <c r="S14" t="n">
-        <v>-184000</v>
+        <v>-2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 주가 상승 억제 및 대차해지 운동 주장.</t>
+          <t>52주 신고가 돌파 기대감 및 주가 고평가 논란. 외국인 및 기관 매매 동향 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '장부 조작']</t>
+          <t>['52주 신고가', '주가 고평가', '외국인 매매']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>317000</v>
+        <v>17610</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.06%</t>
+          <t>'-3.88%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.66</v>
+        <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>120</v>
+        <v>246</v>
       </c>
       <c r="F15" t="n">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="G15" t="n">
-        <v>251</v>
+        <v>1127</v>
       </c>
       <c r="H15" t="n">
-        <v>3.62</v>
+        <v>7.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>327000</v>
+        <v>18320</v>
       </c>
       <c r="K15" t="n">
-        <v>324000</v>
+        <v>18450</v>
       </c>
       <c r="L15" t="n">
-        <v>340500</v>
+        <v>18590</v>
       </c>
       <c r="M15" t="n">
-        <v>308500</v>
+        <v>17560</v>
       </c>
       <c r="N15" t="n">
-        <v>1.96</v>
+        <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>87764341750</v>
+        <v>210928877485</v>
       </c>
       <c r="P15" t="n">
-        <v>635000</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>52600</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-62000</v>
+        <v>-1730000</v>
       </c>
       <c r="S15" t="n">
-        <v>-2000</v>
+        <v>-3000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 후 주가 등락. 외국인 순매수 유입 속 고평가 논란.</t>
+          <t>기관 매수세와 함께 미국 광통신 AI 주식 급등 수혜 기대. 투자주의 종목 지정 및 CB 발행.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['52주 신고가', '외국인 순매수', '고평가 논란']</t>
+          <t>['기관 매수', '광통신 AI', '투자주의']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17620</v>
+        <v>76700</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.82%</t>
+          <t>'-4.12%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="F16" t="n">
-        <v>147</v>
+        <v>86</v>
       </c>
       <c r="G16" t="n">
-        <v>1109</v>
+        <v>756</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>10.58</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18320</v>
+        <v>80000</v>
       </c>
       <c r="K16" t="n">
-        <v>18450</v>
+        <v>82900</v>
       </c>
       <c r="L16" t="n">
-        <v>18590</v>
+        <v>83000</v>
       </c>
       <c r="M16" t="n">
-        <v>17590</v>
+        <v>75300</v>
       </c>
       <c r="N16" t="n">
-        <v>4.61</v>
+        <v>10.68</v>
       </c>
       <c r="O16" t="n">
-        <v>205160891695</v>
+        <v>107563259950</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>184000</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>44750</v>
       </c>
       <c r="R16" t="n">
-        <v>-1730000</v>
+        <v>-556000</v>
       </c>
       <c r="S16" t="n">
-        <v>-3000</v>
+        <v>-46000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대한광통신, 기관 매수세 및 미국 광통신주 급등 영향. 투자주의 종목 지정 및 CB 발행.</t>
+          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['기관매수', '광통신주', '투자주의']</t>
+          <t>['드론', 'K-방산', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4045</v>
+        <v>4035</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.15%</t>
+          <t>'-4.38%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.22</v>
       </c>
       <c r="E17" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="H17" t="n">
         <v>0.33</v>
@@ -1984,13 +1984,13 @@
         <v>4415</v>
       </c>
       <c r="M17" t="n">
-        <v>4030</v>
+        <v>4025</v>
       </c>
       <c r="N17" t="n">
         <v>0.55</v>
       </c>
       <c r="O17" t="n">
-        <v>31031161422</v>
+        <v>31324409992</v>
       </c>
       <c r="P17" t="n">
         <v>6480</v>
@@ -2050,10 +2050,10 @@
         <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G18" t="n">
         <v>184</v>
@@ -2082,7 +2082,7 @@
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>87545901925</v>
+        <v>88273583375</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27750</v>
+        <v>27550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-25.80%</t>
+          <t>'-26.34%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="F19" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G19" t="n">
-        <v>1596</v>
+        <v>1626</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>114498274150</v>
+        <v>115833884175</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>오름테라퓨틱, 임상시험 결과 및 매도 물량 급증으로 하한가 우려. 글로벌 빅파마 협력 기대감.</t>
+          <t>제2 임상시험 결과 발표 예정. 하한가 가능성 언급 및 투자 주의.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상시험', '매도물량', '하한가']</t>
+          <t>['임상시험', '하한가', '매도 물량']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_14.xlsx
+++ b/data/trending_integrated_20260921_14.xlsx
@@ -584,7 +584,7 @@
         <v>132</v>
       </c>
       <c r="G2" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204073409035</v>
+        <v>204127545035</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10800</v>
+        <v>10840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.73%</t>
+          <t>'+20.18%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>249896199340</v>
+        <v>252511284925</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -711,10 +711,10 @@
         <v>3735</v>
       </c>
       <c r="R3" t="n">
-        <v>521000</v>
+        <v>546000</v>
       </c>
       <c r="S3" t="n">
-        <v>59000</v>
+        <v>46000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21250</v>
+        <v>21100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.05%</t>
+          <t>'+14.24%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>110621107895</v>
+        <v>114139014745</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -803,23 +803,23 @@
         <v>9900</v>
       </c>
       <c r="R4" t="n">
-        <v>1000</v>
+        <v>17000</v>
       </c>
       <c r="S4" t="n">
-        <v>43000</v>
+        <v>48000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>혈관 치료 기술 확장 및 글로벌 3상 동시 돌입. 대규모 인수합병 사례 언급.</t>
+          <t>혈관 치료 기술의 전신질환 및 ADC 확장 가능성. MSD의 EyeBio 인수 사례를 바탕으로 한 1조원 베팅 기대감. 글로벌 3상 임상 동시 돌입. 연기금 입성 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['혈관 치료', 'ADC', '인수합병']</t>
+          <t>['ADC 확장', '글로벌 임상', '연기금']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32000</v>
+        <v>32350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.93%</t>
+          <t>'+9.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="F5" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G5" t="n">
-        <v>2184</v>
+        <v>2201</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>38913028675</v>
+        <v>39838700500</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -895,10 +895,10 @@
         <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-192000</v>
+        <v>-134000</v>
       </c>
       <c r="S5" t="n">
-        <v>-7000</v>
+        <v>-4000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5830</v>
+        <v>5810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.37%</t>
+          <t>'+7.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H6" t="n">
         <v>0.19</v>
@@ -978,7 +978,7 @@
         <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>61673048160</v>
+        <v>61904087220</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -987,7 +987,7 @@
         <v>3725</v>
       </c>
       <c r="R6" t="n">
-        <v>-345000</v>
+        <v>-347000</v>
       </c>
       <c r="S6" t="n">
         <v>14000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11190</v>
+        <v>11180</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.37%</t>
+          <t>'+6.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F7" t="n">
         <v>78</v>
       </c>
       <c r="G7" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="H7" t="n">
         <v>18.29</v>
@@ -1070,7 +1070,7 @@
         <v>18.13</v>
       </c>
       <c r="O7" t="n">
-        <v>203098141910</v>
+        <v>204038265485</v>
       </c>
       <c r="P7" t="n">
         <v>22450</v>
@@ -1130,13 +1130,13 @@
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="H8" t="n">
         <v>75.44</v>
@@ -1162,7 +1162,7 @@
         <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>701027871300</v>
+        <v>715553358300</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1171,10 +1171,10 @@
         <v>64700</v>
       </c>
       <c r="R8" t="n">
-        <v>652000</v>
+        <v>677000</v>
       </c>
       <c r="S8" t="n">
-        <v>-2000</v>
+        <v>4000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>273000</v>
+        <v>272750</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.60%</t>
+          <t>'+4.50%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G9" t="n">
-        <v>2642</v>
+        <v>2618</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4702624235500</v>
+        <v>4837445847250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1263,23 +1263,23 @@
         <v>81100</v>
       </c>
       <c r="R9" t="n">
-        <v>5146000</v>
+        <v>5696000</v>
       </c>
       <c r="S9" t="n">
-        <v>1095000</v>
+        <v>1407000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 확인 및 배당금 지급 예정. 증권사 목표가 하향 조정.</t>
+          <t>외국인 대량 매수세 유입 및 배당금 지급 기대감. BNK증권의 목표가 하향에도 불구하고 긍정적 전망. 3분기 잠정실적 발표 및 4분기 자사주 소각·배당 이벤트 예정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 매수', '배당금', '목표가']</t>
+          <t>['외국인 매수', '배당금', '실적 발표']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1871000</v>
+        <v>1867000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.75%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="G10" t="n">
-        <v>2267</v>
+        <v>2244</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3754813832000</v>
+        <v>3868864324500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1355,10 +1355,10 @@
         <v>333000</v>
       </c>
       <c r="R10" t="n">
-        <v>-62000</v>
+        <v>-86000</v>
       </c>
       <c r="S10" t="n">
-        <v>139000</v>
+        <v>153000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26150</v>
+        <v>26300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.43%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>122050446600</v>
+        <v>123303237650</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1447,10 +1447,10 @@
         <v>1030</v>
       </c>
       <c r="R11" t="n">
-        <v>-234000</v>
+        <v>-239000</v>
       </c>
       <c r="S11" t="n">
-        <v>-37000</v>
+        <v>-82000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1483,92 +1483,92 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13480</v>
+        <v>318000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.81%</t>
+          <t>'-2.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58</v>
+        <v>1.66</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="G12" t="n">
-        <v>415</v>
+        <v>268</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>3.62</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13870</v>
+        <v>327000</v>
       </c>
       <c r="K12" t="n">
-        <v>14070</v>
+        <v>324000</v>
       </c>
       <c r="L12" t="n">
-        <v>14790</v>
+        <v>340500</v>
       </c>
       <c r="M12" t="n">
-        <v>13460</v>
+        <v>308500</v>
       </c>
       <c r="N12" t="n">
-        <v>4.92</v>
+        <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>70601625720</v>
+        <v>90146776000</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>635000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>52600</v>
       </c>
       <c r="R12" t="n">
-        <v>-306000</v>
+        <v>-66000</v>
       </c>
       <c r="S12" t="n">
-        <v>-8000</v>
+        <v>-3000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>52주 신고가 돌파 기대감 및 주가 고평가 논란. 외국인 및 기관 매매 동향 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['52주 신고가', '주가 고평가', '외국인 매매']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F13" t="n">
         <v>58</v>
       </c>
       <c r="G13" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>74869712160</v>
+        <v>75813819320</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1631,10 +1631,10 @@
         <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-698000</v>
+        <v>-692000</v>
       </c>
       <c r="S13" t="n">
-        <v>-184000</v>
+        <v>-236000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1667,92 +1667,92 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>317250</v>
+        <v>13450</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.98%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.66</v>
+        <v>0.58</v>
       </c>
       <c r="E14" t="n">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>256</v>
+        <v>423</v>
       </c>
       <c r="H14" t="n">
-        <v>3.62</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>327000</v>
+        <v>13870</v>
       </c>
       <c r="K14" t="n">
-        <v>324000</v>
+        <v>14070</v>
       </c>
       <c r="L14" t="n">
-        <v>340500</v>
+        <v>14790</v>
       </c>
       <c r="M14" t="n">
-        <v>308500</v>
+        <v>13430</v>
       </c>
       <c r="N14" t="n">
-        <v>1.96</v>
+        <v>4.92</v>
       </c>
       <c r="O14" t="n">
-        <v>89249039000</v>
+        <v>71661605205</v>
       </c>
       <c r="P14" t="n">
-        <v>635000</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>52600</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>-62000</v>
+        <v>-382000</v>
       </c>
       <c r="S14" t="n">
-        <v>-2000</v>
+        <v>-14000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 기대감 및 주가 고평가 논란. 외국인 및 기관 매매 동향 언급.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['52주 신고가', '주가 고평가', '외국인 매매']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17610</v>
+        <v>17635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.88%</t>
+          <t>'-3.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F15" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G15" t="n">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>210928877485</v>
+        <v>212753081200</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1815,10 +1815,10 @@
         <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-1730000</v>
+        <v>-1816000</v>
       </c>
       <c r="S15" t="n">
-        <v>-3000</v>
+        <v>-4000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>76700</v>
+        <v>77000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.12%</t>
+          <t>'-3.75%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F16" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>756</v>
+        <v>775</v>
       </c>
       <c r="H16" t="n">
         <v>10.58</v>
@@ -1898,7 +1898,7 @@
         <v>10.68</v>
       </c>
       <c r="O16" t="n">
-        <v>107563259950</v>
+        <v>109740732850</v>
       </c>
       <c r="P16" t="n">
         <v>184000</v>
@@ -1907,10 +1907,10 @@
         <v>44750</v>
       </c>
       <c r="R16" t="n">
-        <v>-556000</v>
+        <v>-598000</v>
       </c>
       <c r="S16" t="n">
-        <v>-46000</v>
+        <v>-21000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1943,70 +1943,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4035</v>
+        <v>30000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.38%</t>
+          <t>'-4.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.22</v>
+        <v>0.48</v>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G17" t="n">
-        <v>389</v>
+        <v>190</v>
       </c>
       <c r="H17" t="n">
-        <v>0.33</v>
+        <v>11.92</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4220</v>
+        <v>31450</v>
       </c>
       <c r="K17" t="n">
-        <v>4220</v>
+        <v>31500</v>
       </c>
       <c r="L17" t="n">
-        <v>4415</v>
+        <v>31550</v>
       </c>
       <c r="M17" t="n">
-        <v>4025</v>
+        <v>29800</v>
       </c>
       <c r="N17" t="n">
-        <v>0.55</v>
+        <v>11.44</v>
       </c>
       <c r="O17" t="n">
-        <v>31324409992</v>
+        <v>88980638000</v>
       </c>
       <c r="P17" t="n">
-        <v>6480</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>1738</v>
+        <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>242000</v>
+        <v>-758000</v>
       </c>
       <c r="S17" t="n">
-        <v>-1000</v>
+        <v>-16000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
+          <t>외인 및 프로그램 매도세 지속, 28000원 복귀 및 급락 가능성. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
+          <t>['매도', '급락', '반도체']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29950</v>
+        <v>4020</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-4.74%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.48</v>
+        <v>-0.22</v>
       </c>
       <c r="E18" t="n">
         <v>103</v>
       </c>
       <c r="F18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>184</v>
+        <v>403</v>
       </c>
       <c r="H18" t="n">
-        <v>11.92</v>
+        <v>0.33</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31450</v>
+        <v>4220</v>
       </c>
       <c r="K18" t="n">
-        <v>31500</v>
+        <v>4220</v>
       </c>
       <c r="L18" t="n">
-        <v>31550</v>
+        <v>4415</v>
       </c>
       <c r="M18" t="n">
-        <v>29800</v>
+        <v>4010</v>
       </c>
       <c r="N18" t="n">
-        <v>11.44</v>
+        <v>0.55</v>
       </c>
       <c r="O18" t="n">
-        <v>88273583375</v>
+        <v>31705210337</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>6480</v>
       </c>
       <c r="Q18" t="n">
-        <v>15000</v>
+        <v>1738</v>
       </c>
       <c r="R18" t="n">
-        <v>-662000</v>
+        <v>264000</v>
       </c>
       <c r="S18" t="n">
-        <v>-9000</v>
+        <v>-4000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외인 및 프로그램 매도세 지속, 28000원 복귀 및 급락 가능성. 투자 심리 위축.</t>
+          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['매도', '급락', '반도체']</t>
+          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27550</v>
+        <v>27500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-26.34%</t>
+          <t>'-26.47%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
         <v>395</v>
       </c>
       <c r="G19" t="n">
-        <v>1626</v>
+        <v>1600</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>115833884175</v>
+        <v>117147356225</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2183,23 +2183,23 @@
         <v>26200</v>
       </c>
       <c r="R19" t="n">
-        <v>218000</v>
+        <v>135000</v>
       </c>
       <c r="S19" t="n">
-        <v>-23000</v>
+        <v>-38000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>제2 임상시험 결과 발표 예정. 하한가 가능성 언급 및 투자 주의.</t>
+          <t>제2임상시험 결과 발표 이후 매도 물량 증가 및 하한가 우려. 대규모 매수세와 약해지는 매수세의 상반된 신호. 종가 하한가 가능성 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상시험', '하한가', '매도 물량']</t>
+          <t>['임상 결과', '매도 물량', '하한가']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_14.xlsx
+++ b/data/trending_integrated_20260921_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204127545035</v>
+        <v>204150598285</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 타임지 선정 '세계 최고 헬스테크 기업' 그룹 선정 소식 기반 주가 급등. 10방 뉴스 및 쩜상 기대감. 단기 반등 후 재하락 가능성 경고.</t>
+          <t>美 타임지 선정 '세계 최고 헬스테크 기업' 그룹 선정. 2주간의 폭락 후 반등 조짐.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지 선정', '급등']</t>
+          <t>['헬스테크', '타임지 선정', '주가 반등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10840</v>
+        <v>10770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.18%</t>
+          <t>'+19.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>252511284925</v>
+        <v>255263888520</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -711,10 +711,10 @@
         <v>3735</v>
       </c>
       <c r="R3" t="n">
-        <v>546000</v>
+        <v>540000</v>
       </c>
       <c r="S3" t="n">
-        <v>46000</v>
+        <v>58000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -762,13 +762,13 @@
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>114139014745</v>
+        <v>115550280495</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>혈관 치료 기술의 전신질환 및 ADC 확장 가능성. MSD의 EyeBio 인수 사례를 바탕으로 한 1조원 베팅 기대감. 글로벌 3상 임상 동시 돌입. 연기금 입성 확인.</t>
+          <t>혈관 치료 기술 확장 및 글로벌 3상 동시 돌입 전망. MSD의 EyeBio 인수 사례 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['ADC 확장', '글로벌 임상', '연기금']</t>
+          <t>['ADC 확장', '글로벌 3상', 'MSD 인수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32350</v>
+        <v>32500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.11%</t>
+          <t>'+9.61%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F5" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G5" t="n">
-        <v>2201</v>
+        <v>2241</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>39838700500</v>
+        <v>41590930050</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -895,7 +895,7 @@
         <v>24150</v>
       </c>
       <c r="R5" t="n">
-        <v>-134000</v>
+        <v>-133000</v>
       </c>
       <c r="S5" t="n">
         <v>-4000</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5810</v>
+        <v>5850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.00%</t>
+          <t>'+7.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="H6" t="n">
         <v>0.19</v>
@@ -978,7 +978,7 @@
         <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>61904087220</v>
+        <v>62011588010</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -990,7 +990,7 @@
         <v>-347000</v>
       </c>
       <c r="S6" t="n">
-        <v>14000</v>
+        <v>26000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11180</v>
+        <v>11160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.27%</t>
+          <t>'+6.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="H7" t="n">
         <v>18.29</v>
@@ -1070,7 +1070,7 @@
         <v>18.13</v>
       </c>
       <c r="O7" t="n">
-        <v>204038265485</v>
+        <v>205378445025</v>
       </c>
       <c r="P7" t="n">
         <v>22450</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>광통신주 급등 및 연기금 매수세 유입. 공시 기대감 속 11500원 돌파 및 2만원 목표.</t>
+          <t>11500원 돌파 시 고점 돌파 전망. 공시 기대감 및 연기금 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '연기금', '공시']</t>
+          <t>['공시', '연기금', '매물대']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>208000</v>
+        <v>207750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+5.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="H8" t="n">
         <v>75.44</v>
@@ -1162,7 +1162,7 @@
         <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>715553358300</v>
+        <v>727742176550</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1174,7 +1174,7 @@
         <v>677000</v>
       </c>
       <c r="S8" t="n">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>272750</v>
+        <v>272500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.50%</t>
+          <t>'+4.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G9" t="n">
-        <v>2618</v>
+        <v>2601</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4837445847250</v>
+        <v>4938333719500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1263,14 +1263,14 @@
         <v>81100</v>
       </c>
       <c r="R9" t="n">
-        <v>5696000</v>
+        <v>5703000</v>
       </c>
       <c r="S9" t="n">
-        <v>1407000</v>
+        <v>1431000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인 대량 매수세 유입 및 배당금 지급 기대감. BNK증권의 목표가 하향에도 불구하고 긍정적 전망. 3분기 잠정실적 발표 및 4분기 자사주 소각·배당 이벤트 예정.</t>
+          <t>외국인 대량 매수에 따른 주가 상승 기대감. 3분기 잠정실적 발표 및 자사주 소각·배당 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외국인 매수', '배당금', '실적 발표']</t>
+          <t>['외국인 매수', '자사주 소각', '배당']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1867000</v>
+        <v>1865000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G10" t="n">
-        <v>2244</v>
+        <v>2307</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3868864324500</v>
+        <v>3950501983000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1355,23 +1355,23 @@
         <v>333000</v>
       </c>
       <c r="R10" t="n">
-        <v>-86000</v>
+        <v>-87000</v>
       </c>
       <c r="S10" t="n">
         <v>153000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>반도체 수출 호조 기대감 속 개인 투자자 매도에 대한 언급. 증권사 앱 오류 발생.</t>
+          <t>개인 매물대 소화 후 상승 기대. 190만 돌파 시 추가 상승 전망. 신한증권 시스템 문제 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체 수출', '개인 매도', '증권사 앱']</t>
+          <t>['반도체 수출', '매물대', '신한증권']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>123303237650</v>
+        <v>124281864150</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1447,7 +1447,7 @@
         <v>1030</v>
       </c>
       <c r="R11" t="n">
-        <v>-239000</v>
+        <v>-240000</v>
       </c>
       <c r="S11" t="n">
         <v>-82000</v>
@@ -1483,103 +1483,103 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>318000</v>
+        <v>13480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-2.81%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.66</v>
+        <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>268</v>
+        <v>434</v>
       </c>
       <c r="H12" t="n">
-        <v>3.62</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>327000</v>
+        <v>13870</v>
       </c>
       <c r="K12" t="n">
-        <v>324000</v>
+        <v>14070</v>
       </c>
       <c r="L12" t="n">
-        <v>340500</v>
+        <v>14790</v>
       </c>
       <c r="M12" t="n">
-        <v>308500</v>
+        <v>13430</v>
       </c>
       <c r="N12" t="n">
-        <v>1.96</v>
+        <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>90146776000</v>
+        <v>72274616145</v>
       </c>
       <c r="P12" t="n">
-        <v>635000</v>
+        <v>30200</v>
       </c>
       <c r="Q12" t="n">
-        <v>52600</v>
+        <v>3540</v>
       </c>
       <c r="R12" t="n">
-        <v>-66000</v>
+        <v>-382000</v>
       </c>
       <c r="S12" t="n">
-        <v>-3000</v>
+        <v>-14000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 기대감 및 주가 고평가 논란. 외국인 및 기관 매매 동향 언급.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['52주 신고가', '주가 고평가', '외국인 매매']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18360</v>
+        <v>317500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1587,19 +1587,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="E13" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F13" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="G13" t="n">
-        <v>443</v>
+        <v>277</v>
       </c>
       <c r="H13" t="n">
-        <v>10.74</v>
+        <v>3.62</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,130 +1607,130 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18910</v>
+        <v>327000</v>
       </c>
       <c r="K13" t="n">
-        <v>19050</v>
+        <v>324000</v>
       </c>
       <c r="L13" t="n">
-        <v>19050</v>
+        <v>340500</v>
       </c>
       <c r="M13" t="n">
-        <v>18090</v>
+        <v>308500</v>
       </c>
       <c r="N13" t="n">
-        <v>10.74</v>
+        <v>1.96</v>
       </c>
       <c r="O13" t="n">
-        <v>75813819320</v>
+        <v>92359227250</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>635000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>52600</v>
       </c>
       <c r="R13" t="n">
-        <v>-692000</v>
+        <v>-66000</v>
       </c>
       <c r="S13" t="n">
-        <v>-236000</v>
+        <v>-3000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 주가 상승 억제 및 대차해지 운동 주장.</t>
+          <t>52주 신고가 돌파 및 40만원 이상 상승 전망. 기관 목표가 상향 조정.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '장부 조작']</t>
+          <t>['신고가 돌파', '기관 목표가', '시총']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13450</v>
+        <v>18320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-3.12%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G14" t="n">
-        <v>423</v>
+        <v>464</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5</v>
+        <v>10.74</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13870</v>
+        <v>18910</v>
       </c>
       <c r="K14" t="n">
-        <v>14070</v>
+        <v>19050</v>
       </c>
       <c r="L14" t="n">
-        <v>14790</v>
+        <v>19050</v>
       </c>
       <c r="M14" t="n">
-        <v>13430</v>
+        <v>18090</v>
       </c>
       <c r="N14" t="n">
-        <v>4.92</v>
+        <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>71661605205</v>
+        <v>78573292390</v>
       </c>
       <c r="P14" t="n">
-        <v>30200</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>3540</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-382000</v>
+        <v>-699000</v>
       </c>
       <c r="S14" t="n">
-        <v>-14000</v>
+        <v>-239000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 주가 상승 억제 및 대차해지 운동 주장.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['공매도', '대차해지', '장부 조작']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17635</v>
+        <v>17660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.74%</t>
+          <t>'-3.60%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F15" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G15" t="n">
-        <v>1130</v>
+        <v>1142</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>212753081200</v>
+        <v>214392682745</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1815,7 +1815,7 @@
         <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-1816000</v>
+        <v>-1828000</v>
       </c>
       <c r="S15" t="n">
         <v>-4000</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>77000</v>
+        <v>76800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.75%</t>
+          <t>'-4.00%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" t="n">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="H16" t="n">
         <v>10.58</v>
@@ -1898,7 +1898,7 @@
         <v>10.68</v>
       </c>
       <c r="O16" t="n">
-        <v>109740732850</v>
+        <v>111452120300</v>
       </c>
       <c r="P16" t="n">
         <v>184000</v>
@@ -1907,23 +1907,23 @@
         <v>44750</v>
       </c>
       <c r="R16" t="n">
-        <v>-598000</v>
+        <v>-605000</v>
       </c>
       <c r="S16" t="n">
-        <v>-21000</v>
+        <v>-17000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유럽 드론 시장 진출 기대감 속 K-방산 경쟁력 부각. 필리조선소 매각 및 공매도 관련 언급.</t>
+          <t>K-방산 '다층 대드론' 새 시장 개척 기대. 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['드론', 'K-방산', '공매도']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1961,7 +1961,7 @@
         <v>107</v>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" t="n">
         <v>190</v>
@@ -1990,7 +1990,7 @@
         <v>11.44</v>
       </c>
       <c r="O17" t="n">
-        <v>88980638000</v>
+        <v>89810315500</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -1999,7 +1999,7 @@
         <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>-758000</v>
+        <v>-759000</v>
       </c>
       <c r="S17" t="n">
         <v>-16000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.74%</t>
+          <t>'-4.98%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.22</v>
       </c>
       <c r="E18" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="H18" t="n">
         <v>0.33</v>
@@ -2076,13 +2076,13 @@
         <v>4415</v>
       </c>
       <c r="M18" t="n">
-        <v>4010</v>
+        <v>4005</v>
       </c>
       <c r="N18" t="n">
         <v>0.55</v>
       </c>
       <c r="O18" t="n">
-        <v>31705210337</v>
+        <v>31955544922</v>
       </c>
       <c r="P18" t="n">
         <v>6480</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27500</v>
+        <v>27350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-26.47%</t>
+          <t>'-26.87%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G19" t="n">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>117147356225</v>
+        <v>117860738100</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2186,20 +2186,20 @@
         <v>135000</v>
       </c>
       <c r="S19" t="n">
-        <v>-38000</v>
+        <v>-49000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>제2임상시험 결과 발표 이후 매도 물량 증가 및 하한가 우려. 대규모 매수세와 약해지는 매수세의 상반된 신호. 종가 하한가 가능성 제기.</t>
+          <t>임상 2상 결과 발표 예정. 매도 물량 증가 및 하한가 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상 결과', '매도 물량', '하한가']</t>
+          <t>['임상 2상', '매도 물량', '하한가']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_14.xlsx
+++ b/data/trending_integrated_20260921_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F2" t="n">
         <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204150598285</v>
+        <v>204207360285</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10770</v>
+        <v>10690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.40%</t>
+          <t>'+18.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G3" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>255263888520</v>
+        <v>259628975460</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21100</v>
+        <v>21200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.24%</t>
+          <t>'+14.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>115550280495</v>
+        <v>117732797145</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>혈관 치료 기술 확장 및 글로벌 3상 동시 돌입 전망. MSD의 EyeBio 인수 사례 언급.</t>
+          <t>국내 유일 혈관 치료 기술의 전신 질환 및 ADC 확장 가능성에 대한 기대감. MSD의 EyeBio 인수 사례 비교 및 글로벌 3상 동시 돌입 소식.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['ADC 확장', '글로벌 3상', 'MSD 인수']</t>
+          <t>['혈관 치료', 'ADC 확장', '글로벌 3상']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32500</v>
+        <v>32300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.61%</t>
+          <t>'+8.94%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F5" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="G5" t="n">
-        <v>2241</v>
+        <v>2245</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>41590930050</v>
+        <v>42419844650</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HLB, FDA 신약 승인 과정 및 제품명 조건부 수용 논의. 담관암 관련 불확실성 및 과거 패턴 반복 우려.</t>
+          <t>FDA 신약 승인 기대감 속에서 조건부 수용 및 NDA 통과 관련 논의. 담관암 임상 결과 및 외국인 매도세에 대한 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA승인', '담관암', '신약']</t>
+          <t>['FDA 승인', 'NDA 통과', '담관암 임상']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5850</v>
+        <v>5890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.73%</t>
+          <t>'+8.47%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.31</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H6" t="n">
         <v>0.19</v>
@@ -978,7 +978,7 @@
         <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>62011588010</v>
+        <v>62387251780</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11160</v>
+        <v>207500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.08%</t>
+          <t>'+5.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G7" t="n">
-        <v>452</v>
+        <v>586</v>
       </c>
       <c r="H7" t="n">
-        <v>18.29</v>
+        <v>75.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10520</v>
+        <v>196100</v>
       </c>
       <c r="K7" t="n">
-        <v>10780</v>
+        <v>199800</v>
       </c>
       <c r="L7" t="n">
-        <v>12190</v>
+        <v>209000</v>
       </c>
       <c r="M7" t="n">
-        <v>10590</v>
+        <v>199600</v>
       </c>
       <c r="N7" t="n">
-        <v>18.13</v>
+        <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>205378445025</v>
+        <v>736571021050</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>64700</v>
       </c>
       <c r="R7" t="n">
-        <v>-70000</v>
+        <v>677000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11500원 돌파 시 고점 돌파 전망. 공시 기대감 및 연기금 매수세 유입.</t>
+          <t>외인 수급 집중 및 연말 배당 기대감. 52주 신고가 돌파 및 30만원 목표.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공시', '연기금', '매물대']</t>
+          <t>['우선주', '외인 수급', '배당 기대']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>207750</v>
+        <v>11110</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.94%</t>
+          <t>'+5.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.09</v>
+        <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>569</v>
+        <v>454</v>
       </c>
       <c r="H8" t="n">
-        <v>75.44</v>
+        <v>18.29</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>196100</v>
+        <v>10520</v>
       </c>
       <c r="K8" t="n">
-        <v>199800</v>
+        <v>10780</v>
       </c>
       <c r="L8" t="n">
-        <v>209000</v>
+        <v>12190</v>
       </c>
       <c r="M8" t="n">
-        <v>199600</v>
+        <v>10590</v>
       </c>
       <c r="N8" t="n">
-        <v>75.53</v>
+        <v>18.13</v>
       </c>
       <c r="O8" t="n">
-        <v>727742176550</v>
+        <v>206463537645</v>
       </c>
       <c r="P8" t="n">
-        <v>243500</v>
+        <v>22450</v>
       </c>
       <c r="Q8" t="n">
-        <v>64700</v>
+        <v>1760</v>
       </c>
       <c r="R8" t="n">
-        <v>677000</v>
+        <v>-70000</v>
       </c>
       <c r="S8" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>외인 수급 집중 및 연말 배당 기대감. 52주 신고가 돌파 및 30만원 목표.</t>
+          <t>11500원 돌파 시 고점 돌파 전망. 공시 기대감 및 연기금 매수세 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['우선주', '외인 수급', '배당 기대']</t>
+          <t>['공시', '연기금', '매물대']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>272500</v>
+        <v>273000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.41%</t>
+          <t>'+4.60%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G9" t="n">
-        <v>2601</v>
+        <v>2534</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>4938333719500</v>
+        <v>5056705752500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인 대량 매수에 따른 주가 상승 기대감. 3분기 잠정실적 발표 및 자사주 소각·배당 관련 언급.</t>
+          <t>외국인 대량 매수세 유입 속에서 배당금 및 자사주 소각/배당 관련 기대감 형성. BNK증권의 목표가 하향 조정 속에서도 주가 상승에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외국인 매수', '자사주 소각', '배당']</t>
+          <t>['외인 매수', '배당금', '자사주 소각']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1865000</v>
+        <v>1868500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>500</v>
       </c>
       <c r="G10" t="n">
-        <v>2307</v>
+        <v>2336</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3950501983000</v>
+        <v>4043250999500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26300</v>
+        <v>26250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-2.05%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
         <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>124281864150</v>
+        <v>125208958800</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13480</v>
+        <v>316500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.81%</t>
+          <t>'-3.21%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58</v>
+        <v>1.66</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="G12" t="n">
-        <v>434</v>
+        <v>291</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>3.62</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13870</v>
+        <v>327000</v>
       </c>
       <c r="K12" t="n">
-        <v>14070</v>
+        <v>324000</v>
       </c>
       <c r="L12" t="n">
-        <v>14790</v>
+        <v>340500</v>
       </c>
       <c r="M12" t="n">
-        <v>13430</v>
+        <v>308500</v>
       </c>
       <c r="N12" t="n">
-        <v>4.92</v>
+        <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>72274616145</v>
+        <v>93307284750</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>635000</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>52600</v>
       </c>
       <c r="R12" t="n">
-        <v>-382000</v>
+        <v>-66000</v>
       </c>
       <c r="S12" t="n">
-        <v>-14000</v>
+        <v>-3000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>52주 신고가 돌파 및 기관 목표가 상향 조정 가능성에 대한 기대감. 외국인 순매수세 유입으로 인한 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['신고가 돌파', '기관 목표가', '외국인 순매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>317500</v>
+        <v>13420</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.91%</t>
+          <t>'-3.24%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.66</v>
+        <v>0.58</v>
       </c>
       <c r="E13" t="n">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="G13" t="n">
-        <v>277</v>
+        <v>439</v>
       </c>
       <c r="H13" t="n">
-        <v>3.62</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>327000</v>
+        <v>13870</v>
       </c>
       <c r="K13" t="n">
-        <v>324000</v>
+        <v>14070</v>
       </c>
       <c r="L13" t="n">
-        <v>340500</v>
+        <v>14790</v>
       </c>
       <c r="M13" t="n">
-        <v>308500</v>
+        <v>13420</v>
       </c>
       <c r="N13" t="n">
-        <v>1.96</v>
+        <v>4.92</v>
       </c>
       <c r="O13" t="n">
-        <v>92359227250</v>
+        <v>73077534030</v>
       </c>
       <c r="P13" t="n">
-        <v>635000</v>
+        <v>30200</v>
       </c>
       <c r="Q13" t="n">
-        <v>52600</v>
+        <v>3540</v>
       </c>
       <c r="R13" t="n">
-        <v>-66000</v>
+        <v>-382000</v>
       </c>
       <c r="S13" t="n">
-        <v>-3000</v>
+        <v>-14000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 및 40만원 이상 상승 전망. 기관 목표가 상향 조정.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['신고가 돌파', '기관 목표가', '시총']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18320</v>
+        <v>18260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.12%</t>
+          <t>'-3.44%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F14" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>78573292390</v>
+        <v>80978857570</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17660</v>
+        <v>17600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.60%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F15" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G15" t="n">
-        <v>1142</v>
+        <v>1158</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>214392682745</v>
+        <v>216258242165</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1851,123 +1851,123 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>76800</v>
+        <v>4045</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-4.15%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="F16" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>784</v>
+        <v>414</v>
       </c>
       <c r="H16" t="n">
-        <v>10.58</v>
+        <v>0.33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>80000</v>
+        <v>4220</v>
       </c>
       <c r="K16" t="n">
-        <v>82900</v>
+        <v>4220</v>
       </c>
       <c r="L16" t="n">
-        <v>83000</v>
+        <v>4415</v>
       </c>
       <c r="M16" t="n">
-        <v>75300</v>
+        <v>4005</v>
       </c>
       <c r="N16" t="n">
-        <v>10.68</v>
+        <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>111452120300</v>
+        <v>32129250794</v>
       </c>
       <c r="P16" t="n">
-        <v>184000</v>
+        <v>6480</v>
       </c>
       <c r="Q16" t="n">
-        <v>44750</v>
+        <v>1738</v>
       </c>
       <c r="R16" t="n">
-        <v>-605000</v>
+        <v>264000</v>
       </c>
       <c r="S16" t="n">
-        <v>-17000</v>
+        <v>-4000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>K-방산 '다층 대드론' 새 시장 개척 기대. 공매도 관련 부정적 언급.</t>
+          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30000</v>
+        <v>76600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.61%</t>
+          <t>'-4.25%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.48</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G17" t="n">
-        <v>190</v>
+        <v>784</v>
       </c>
       <c r="H17" t="n">
-        <v>11.92</v>
+        <v>10.58</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,130 +1975,130 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>31450</v>
+        <v>80000</v>
       </c>
       <c r="K17" t="n">
-        <v>31500</v>
+        <v>82900</v>
       </c>
       <c r="L17" t="n">
-        <v>31550</v>
+        <v>83000</v>
       </c>
       <c r="M17" t="n">
-        <v>29800</v>
+        <v>75300</v>
       </c>
       <c r="N17" t="n">
-        <v>11.44</v>
+        <v>10.68</v>
       </c>
       <c r="O17" t="n">
-        <v>89810315500</v>
+        <v>113270034100</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>184000</v>
       </c>
       <c r="Q17" t="n">
-        <v>15000</v>
+        <v>44750</v>
       </c>
       <c r="R17" t="n">
-        <v>-759000</v>
+        <v>-605000</v>
       </c>
       <c r="S17" t="n">
-        <v>-16000</v>
+        <v>-17000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외인 및 프로그램 매도세 지속, 28000원 복귀 및 급락 가능성. 투자 심리 위축.</t>
+          <t>K-방산 '다층 대드론' 새 시장 개척 기대. 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['매도', '급락', '반도체']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4010</v>
+        <v>29950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.98%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.22</v>
+        <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G18" t="n">
-        <v>408</v>
+        <v>190</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33</v>
+        <v>11.92</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4220</v>
+        <v>31450</v>
       </c>
       <c r="K18" t="n">
-        <v>4220</v>
+        <v>31500</v>
       </c>
       <c r="L18" t="n">
-        <v>4415</v>
+        <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>4005</v>
+        <v>29800</v>
       </c>
       <c r="N18" t="n">
-        <v>0.55</v>
+        <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>31955544922</v>
+        <v>91392366525</v>
       </c>
       <c r="P18" t="n">
-        <v>6480</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>1738</v>
+        <v>15000</v>
       </c>
       <c r="R18" t="n">
-        <v>264000</v>
+        <v>-759000</v>
       </c>
       <c r="S18" t="n">
-        <v>-4000</v>
+        <v>-16000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
+          <t>외인 및 프로그램 매도세 지속, 28000원 복귀 및 급락 가능성. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
+          <t>['매도', '급락', '반도체']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27350</v>
+        <v>27450</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-26.87%</t>
+          <t>'-26.60%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G19" t="n">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>117860738100</v>
+        <v>118618200750</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>임상 2상 결과 발표 예정. 매도 물량 증가 및 하한가 우려.</t>
+          <t>제2임상시험 결과 발표를 앞두고 매도 물량 증가 및 하한가 가능성 제기. 투자자들의 불안감 및 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상 2상', '매도 물량', '하한가']</t>
+          <t>['임상시험 결과', '매도 물량', '주가 하락']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260921_14.xlsx
+++ b/data/trending_integrated_20260921_14.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F2" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>204207360285</v>
+        <v>204236776535</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10690</v>
+        <v>10740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.51%</t>
+          <t>'+19.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>259628975460</v>
+        <v>263350091475</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21200</v>
+        <v>21500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.78%</t>
+          <t>'+16.40%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F4" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>117732797145</v>
+        <v>123720080845</v>
       </c>
       <c r="P4" t="n">
         <v>21950</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국내 유일 혈관 치료 기술의 전신 질환 및 ADC 확장 가능성에 대한 기대감. MSD의 EyeBio 인수 사례 비교 및 글로벌 3상 동시 돌입 소식.</t>
+          <t>혈관 치료 기술의 전신질환·ADC 확장 및 글로벌 3상 동시 돌입. MSD의 EyeBio 인수에 따른 1조원 베팅 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['혈관 치료', 'ADC 확장', '글로벌 3상']</t>
+          <t>['ADC 확장', '글로벌 3상', '1조원 베팅']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32300</v>
+        <v>32100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.94%</t>
+          <t>'+8.26%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="F5" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G5" t="n">
-        <v>2245</v>
+        <v>2257</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>42419844650</v>
+        <v>42989758000</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5890</v>
+        <v>5860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.47%</t>
+          <t>'+7.92%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,7 +978,7 @@
         <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>62387251780</v>
+        <v>62607712165</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207500</v>
+        <v>208250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.81%</t>
+          <t>'+6.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>69</v>
       </c>
       <c r="G7" t="n">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>736571021050</v>
+        <v>752682581050</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11110</v>
+        <v>11040</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.61%</t>
+          <t>'+4.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" t="n">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="H8" t="n">
         <v>18.29</v>
@@ -1162,7 +1162,7 @@
         <v>18.13</v>
       </c>
       <c r="O8" t="n">
-        <v>206463537645</v>
+        <v>207557063775</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="G9" t="n">
-        <v>2534</v>
+        <v>2511</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>5056705752500</v>
+        <v>5148549869250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외국인 대량 매수세 유입 속에서 배당금 및 자사주 소각/배당 관련 기대감 형성. BNK증권의 목표가 하향 조정 속에서도 주가 상승에 대한 긍정적 전망.</t>
+          <t>외인 매수세 유입 및 배당금 기대감 속 주가 상승 전망. 3분기 잠정 실적 발표 및 자사주 소각/배당 이슈 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인 매수', '배당금', '자사주 소각']</t>
+          <t>['외인 매수', '배당금', '실적 발표']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1868500</v>
+        <v>1869000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'+0.65%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G10" t="n">
-        <v>2336</v>
+        <v>2323</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>4043250999500</v>
+        <v>4133049837500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26250</v>
+        <v>26500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.05%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H11" t="n">
         <v>2.11</v>
@@ -1438,7 +1438,7 @@
         <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>125208958800</v>
+        <v>126659773500</v>
       </c>
       <c r="P11" t="n">
         <v>59600</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>316500</v>
+        <v>317500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1.66</v>
       </c>
       <c r="E12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H12" t="n">
         <v>3.62</v>
@@ -1530,7 +1530,7 @@
         <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>93307284750</v>
+        <v>94316098750</v>
       </c>
       <c r="P12" t="n">
         <v>635000</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 및 기관 목표가 상향 조정 가능성에 대한 기대감. 외국인 순매수세 유입으로 인한 상승 추세 전망.</t>
+          <t>52주 신고가 돌파 및 기관 목표가 상향 기대감. 외국인 재유입 신호 감지.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신고가 돌파', '기관 목표가', '외국인 순매수']</t>
+          <t>['52주 신고가', '기관 목표가', '외국인 유입']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,70 +1575,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13420</v>
+        <v>18280</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.24%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="G13" t="n">
-        <v>439</v>
+        <v>497</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>10.74</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>13870</v>
+        <v>18910</v>
       </c>
       <c r="K13" t="n">
-        <v>14070</v>
+        <v>19050</v>
       </c>
       <c r="L13" t="n">
-        <v>14790</v>
+        <v>19050</v>
       </c>
       <c r="M13" t="n">
-        <v>13420</v>
+        <v>18090</v>
       </c>
       <c r="N13" t="n">
-        <v>4.92</v>
+        <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>73077534030</v>
+        <v>82209257770</v>
       </c>
       <c r="P13" t="n">
-        <v>30200</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>3540</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-382000</v>
+        <v>-699000</v>
       </c>
       <c r="S13" t="n">
-        <v>-14000</v>
+        <v>-239000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 주가 상승 억제 및 대차해지 운동 주장.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['공매도', '대차해지', '장부 조작']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,77 +1660,77 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18260</v>
+        <v>13390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.44%</t>
+          <t>'-3.46%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="E14" t="n">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="F14" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18910</v>
+        <v>13870</v>
       </c>
       <c r="K14" t="n">
-        <v>19050</v>
+        <v>14070</v>
       </c>
       <c r="L14" t="n">
-        <v>19050</v>
+        <v>14790</v>
       </c>
       <c r="M14" t="n">
-        <v>18090</v>
+        <v>13370</v>
       </c>
       <c r="N14" t="n">
-        <v>10.74</v>
+        <v>4.92</v>
       </c>
       <c r="O14" t="n">
-        <v>80978857570</v>
+        <v>74568843030</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>30200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>3540</v>
       </c>
       <c r="R14" t="n">
-        <v>-699000</v>
+        <v>-382000</v>
       </c>
       <c r="S14" t="n">
-        <v>-239000</v>
+        <v>-14000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 장부 조작 및 대차 오링 의혹 제기. 주가 상승 억제 및 대차해지 운동 주장.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '장부 조작']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17600</v>
+        <v>77100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-3.62%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>257</v>
+        <v>179</v>
       </c>
       <c r="F15" t="n">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>1158</v>
+        <v>787</v>
       </c>
       <c r="H15" t="n">
-        <v>7.9</v>
+        <v>10.58</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18320</v>
+        <v>80000</v>
       </c>
       <c r="K15" t="n">
-        <v>18450</v>
+        <v>82900</v>
       </c>
       <c r="L15" t="n">
-        <v>18590</v>
+        <v>83000</v>
       </c>
       <c r="M15" t="n">
-        <v>17560</v>
+        <v>75300</v>
       </c>
       <c r="N15" t="n">
-        <v>4.61</v>
+        <v>10.68</v>
       </c>
       <c r="O15" t="n">
-        <v>216258242165</v>
+        <v>115568830750</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>184000</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>44750</v>
       </c>
       <c r="R15" t="n">
-        <v>-1828000</v>
+        <v>-605000</v>
       </c>
       <c r="S15" t="n">
-        <v>-4000</v>
+        <v>-17000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>기관 매수세와 함께 미국 광통신 AI 주식 급등 수혜 기대. 투자주의 종목 지정 및 CB 발행.</t>
+          <t>K-방산 '다층 대드론' 새 시장 개척 기대. 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['기관 매수', '광통신 AI', '투자주의']</t>
+          <t>['K-방산', '드론', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4045</v>
+        <v>17580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.15%</t>
+          <t>'-4.04%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.22</v>
+        <v>3.29</v>
       </c>
       <c r="E16" t="n">
-        <v>106</v>
+        <v>261</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="G16" t="n">
-        <v>414</v>
+        <v>1168</v>
       </c>
       <c r="H16" t="n">
-        <v>0.33</v>
+        <v>7.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,152 +1883,152 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4220</v>
+        <v>18320</v>
       </c>
       <c r="K16" t="n">
-        <v>4220</v>
+        <v>18450</v>
       </c>
       <c r="L16" t="n">
-        <v>4415</v>
+        <v>18590</v>
       </c>
       <c r="M16" t="n">
-        <v>4005</v>
+        <v>17560</v>
       </c>
       <c r="N16" t="n">
-        <v>0.55</v>
+        <v>4.61</v>
       </c>
       <c r="O16" t="n">
-        <v>32129250794</v>
+        <v>218604822325</v>
       </c>
       <c r="P16" t="n">
-        <v>6480</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>1738</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>264000</v>
+        <v>-1828000</v>
       </c>
       <c r="S16" t="n">
         <v>-4000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
+          <t>기관 매수세와 함께 미국 광통신 AI 주식 급등 수혜 기대. 투자주의 종목 지정 및 CB 발행.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
+          <t>['기관 매수', '광통신 AI', '투자주의']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76600</v>
+        <v>4030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.25%</t>
+          <t>'-4.50%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="E17" t="n">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="F17" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="G17" t="n">
-        <v>784</v>
+        <v>435</v>
       </c>
       <c r="H17" t="n">
-        <v>10.58</v>
+        <v>0.33</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>80000</v>
+        <v>4220</v>
       </c>
       <c r="K17" t="n">
-        <v>82900</v>
+        <v>4220</v>
       </c>
       <c r="L17" t="n">
-        <v>83000</v>
+        <v>4415</v>
       </c>
       <c r="M17" t="n">
-        <v>75300</v>
+        <v>4005</v>
       </c>
       <c r="N17" t="n">
-        <v>10.68</v>
+        <v>0.55</v>
       </c>
       <c r="O17" t="n">
-        <v>113270034100</v>
+        <v>32283840331</v>
       </c>
       <c r="P17" t="n">
-        <v>184000</v>
+        <v>6480</v>
       </c>
       <c r="Q17" t="n">
-        <v>44750</v>
+        <v>1738</v>
       </c>
       <c r="R17" t="n">
-        <v>-605000</v>
+        <v>264000</v>
       </c>
       <c r="S17" t="n">
-        <v>-17000</v>
+        <v>-4000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>K-방산 '다층 대드론' 새 시장 개척 기대. 공매도 관련 부정적 언급.</t>
+          <t>재료 대비 주가 부진, 물량 넘기기 및 개잡주 평가. 3840 가격대 기다리며 신규 매수 금지 의견.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['K-방산', '드론', '공매도']</t>
+          <t>['주가 부진', '물량 넘기기', '신규 매수 금지']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29950</v>
+        <v>29900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-4.93%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F18" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18" t="n">
         <v>190</v>
@@ -2082,7 +2082,7 @@
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>91392366525</v>
+        <v>92092994625</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G19" t="n">
-        <v>1593</v>
+        <v>1637</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>118618200750</v>
+        <v>119233966750</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>제2임상시험 결과 발표를 앞두고 매도 물량 증가 및 하한가 가능성 제기. 투자자들의 불안감 및 주가 하락에 대한 우려.</t>
+          <t>주주들 불만 고조 및 상장폐지 우려. 제2임상시험 결과 불확실성 속 매도 물량 증가.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['임상시험 결과', '매도 물량', '주가 하락']</t>
+          <t>['상장폐지', '임상시험 결과', '매도 물량']</t>
         </is>
       </c>
       <c r="X19" t="n">
